--- a/data/Harvest_Timing_ADFG.xlsx
+++ b/data/Harvest_Timing_ADFG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariegutgesell/Desktop/Wild Foods Repo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariegutgesell/LocalRepos/Wild Foods Repo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC71DA35-C3E2-B64C-A975-2D8C0043558B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8875DFB0-CAB9-6942-8825-153277711A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="500" windowWidth="26480" windowHeight="16480" xr2:uid="{B010086E-6C30-FF4F-B539-334CB571F607}"/>
   </bookViews>
@@ -566,288 +566,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -861,9 +580,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -901,7 +620,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1007,7 +726,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1149,7 +868,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1157,7 +876,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30C244E-ED8D-E247-AA44-F3617E2C6815}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P415"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1214,7 +932,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1264,7 +982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1314,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1364,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1414,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1464,7 +1182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1514,7 +1232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1564,7 +1282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1614,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1714,7 +1432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1764,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1814,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1864,7 +1582,7 @@
         <v>2.423841059602649</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1914,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1964,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2014,7 +1732,7 @@
         <v>3.3426827684716272</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2064,7 +1782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2114,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2164,7 +1882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -2214,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -2264,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -2314,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -2364,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -2414,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -2514,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -2564,7 +2282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -2614,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -2664,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -2714,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -2764,7 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -2814,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -2864,7 +2582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -2914,7 +2632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -2964,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -3014,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -3064,7 +2782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -3114,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -3164,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -3214,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -3264,7 +2982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -3314,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -3364,7 +3082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -3414,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -3464,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -3514,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -3564,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -3614,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -3664,7 +3382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -3714,7 +3432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -3764,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -3814,7 +3532,7 @@
         <v>2.392156862745098</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -3864,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -3914,7 +3632,7 @@
         <v>2.392156862745098</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -3964,7 +3682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -4064,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -4114,7 +3832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -4164,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -4214,7 +3932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>88</v>
       </c>
@@ -4264,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>88</v>
       </c>
@@ -4314,7 +4032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>88</v>
       </c>
@@ -4364,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>88</v>
       </c>
@@ -4414,7 +4132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>88</v>
       </c>
@@ -4464,7 +4182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>88</v>
       </c>
@@ -4514,7 +4232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>88</v>
       </c>
@@ -4564,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>88</v>
       </c>
@@ -4614,7 +4332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>88</v>
       </c>
@@ -4664,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -4714,7 +4432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>88</v>
       </c>
@@ -4764,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>88</v>
       </c>
@@ -4814,7 +4532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -4864,7 +4582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -4914,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>88</v>
       </c>
@@ -4964,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -5014,7 +4732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>88</v>
       </c>
@@ -5064,7 +4782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -5114,7 +4832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -5164,7 +4882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -5214,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>88</v>
       </c>
@@ -5264,7 +4982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -5314,7 +5032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>88</v>
       </c>
@@ -5364,7 +5082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -5414,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -5464,7 +5182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -5514,7 +5232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -5564,7 +5282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -5614,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>88</v>
       </c>
@@ -5664,7 +5382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -5714,7 +5432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>88</v>
       </c>
@@ -5764,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>88</v>
       </c>
@@ -5814,7 +5532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -5864,7 +5582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>88</v>
       </c>
@@ -5914,7 +5632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>88</v>
       </c>
@@ -5964,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>88</v>
       </c>
@@ -6014,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>88</v>
       </c>
@@ -6064,7 +5782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>88</v>
       </c>
@@ -6114,7 +5832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>88</v>
       </c>
@@ -6164,7 +5882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>88</v>
       </c>
@@ -6214,7 +5932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>88</v>
       </c>
@@ -6264,7 +5982,7 @@
         <v>123.93939393939394</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>88</v>
       </c>
@@ -6314,7 +6032,7 @@
         <v>18.590909090909093</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>88</v>
       </c>
@@ -6364,7 +6082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>88</v>
       </c>
@@ -6414,7 +6132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>88</v>
       </c>
@@ -6464,7 +6182,7 @@
         <v>24.787878787878789</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>88</v>
       </c>
@@ -6514,7 +6232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>88</v>
       </c>
@@ -6564,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>88</v>
       </c>
@@ -6614,7 +6332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>88</v>
       </c>
@@ -6664,7 +6382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>88</v>
       </c>
@@ -6714,7 +6432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>88</v>
       </c>
@@ -6764,7 +6482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>88</v>
       </c>
@@ -6814,7 +6532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>88</v>
       </c>
@@ -6864,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>88</v>
       </c>
@@ -6914,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>88</v>
       </c>
@@ -6964,7 +6682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>88</v>
       </c>
@@ -7014,7 +6732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -7064,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>88</v>
       </c>
@@ -7164,7 +6882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>88</v>
       </c>
@@ -7214,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>88</v>
       </c>
@@ -7264,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -7314,7 +7032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>96</v>
       </c>
@@ -7364,7 +7082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>96</v>
       </c>
@@ -7414,7 +7132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>96</v>
       </c>
@@ -7464,7 +7182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>96</v>
       </c>
@@ -7514,7 +7232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>96</v>
       </c>
@@ -7564,7 +7282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>96</v>
       </c>
@@ -7614,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>96</v>
       </c>
@@ -7664,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>96</v>
       </c>
@@ -7714,7 +7432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>96</v>
       </c>
@@ -7764,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>96</v>
       </c>
@@ -7814,7 +7532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>96</v>
       </c>
@@ -7864,7 +7582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>96</v>
       </c>
@@ -7914,7 +7632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>96</v>
       </c>
@@ -7964,7 +7682,7 @@
         <v>32.219178082191782</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>96</v>
       </c>
@@ -8014,7 +7732,7 @@
         <v>29.83606557377049</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>96</v>
       </c>
@@ -8064,7 +7782,7 @@
         <v>2.2950819672131146</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>96</v>
       </c>
@@ -8114,7 +7832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>96</v>
       </c>
@@ -8164,7 +7882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>96</v>
       </c>
@@ -8214,7 +7932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>96</v>
       </c>
@@ -8264,7 +7982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>96</v>
       </c>
@@ -8314,7 +8032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>96</v>
       </c>
@@ -8364,7 +8082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>96</v>
       </c>
@@ -8414,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>96</v>
       </c>
@@ -8464,7 +8182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>96</v>
       </c>
@@ -8514,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>96</v>
       </c>
@@ -8564,7 +8282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>96</v>
       </c>
@@ -8614,7 +8332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>96</v>
       </c>
@@ -8664,7 +8382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>96</v>
       </c>
@@ -8714,7 +8432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>96</v>
       </c>
@@ -8764,7 +8482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>96</v>
       </c>
@@ -8814,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>96</v>
       </c>
@@ -8864,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>96</v>
       </c>
@@ -8914,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>96</v>
       </c>
@@ -8964,7 +8682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>96</v>
       </c>
@@ -9014,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>96</v>
       </c>
@@ -9064,7 +8782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>96</v>
       </c>
@@ -9114,7 +8832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>96</v>
       </c>
@@ -9164,7 +8882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>96</v>
       </c>
@@ -9214,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>96</v>
       </c>
@@ -9264,7 +8982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>96</v>
       </c>
@@ -9314,7 +9032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>96</v>
       </c>
@@ -9364,7 +9082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>96</v>
       </c>
@@ -9414,7 +9132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>96</v>
       </c>
@@ -9464,7 +9182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>96</v>
       </c>
@@ -9514,7 +9232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>96</v>
       </c>
@@ -9564,7 +9282,7 @@
         <v>2.2950819672131146</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>96</v>
       </c>
@@ -9614,7 +9332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>96</v>
       </c>
@@ -9664,7 +9382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>96</v>
       </c>
@@ -9714,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>96</v>
       </c>
@@ -9764,7 +9482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>96</v>
       </c>
@@ -9814,7 +9532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>96</v>
       </c>
@@ -9864,7 +9582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>96</v>
       </c>
@@ -9914,7 +9632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>96</v>
       </c>
@@ -9964,7 +9682,7 @@
         <v>48.196721311475422</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>96</v>
       </c>
@@ -10014,7 +9732,7 @@
         <v>18.360655737704917</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>96</v>
       </c>
@@ -10064,7 +9782,7 @@
         <v>2.2950819672131146</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>96</v>
       </c>
@@ -10114,7 +9832,7 @@
         <v>27.540983606557376</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>96</v>
       </c>
@@ -10214,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>96</v>
       </c>
@@ -10264,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>96</v>
       </c>
@@ -10314,7 +10032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>96</v>
       </c>
@@ -10364,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>97</v>
       </c>
@@ -10414,7 +10132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>97</v>
       </c>
@@ -10464,7 +10182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>97</v>
       </c>
@@ -10514,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>97</v>
       </c>
@@ -10564,7 +10282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>97</v>
       </c>
@@ -10614,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>97</v>
       </c>
@@ -10664,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>97</v>
       </c>
@@ -10714,7 +10432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>97</v>
       </c>
@@ -10764,7 +10482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>97</v>
       </c>
@@ -10814,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>97</v>
       </c>
@@ -10864,7 +10582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>97</v>
       </c>
@@ -10914,7 +10632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>97</v>
       </c>
@@ -10964,7 +10682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>97</v>
       </c>
@@ -11014,7 +10732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>97</v>
       </c>
@@ -11064,7 +10782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>97</v>
       </c>
@@ -11114,7 +10832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>97</v>
       </c>
@@ -11164,7 +10882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>97</v>
       </c>
@@ -11214,7 +10932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>97</v>
       </c>
@@ -11264,7 +10982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>97</v>
       </c>
@@ -11314,7 +11032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>97</v>
       </c>
@@ -11364,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>97</v>
       </c>
@@ -11414,7 +11132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>97</v>
       </c>
@@ -11464,7 +11182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -11514,7 +11232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>97</v>
       </c>
@@ -11564,7 +11282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>97</v>
       </c>
@@ -11614,7 +11332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>97</v>
       </c>
@@ -11664,7 +11382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>97</v>
       </c>
@@ -11714,7 +11432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>97</v>
       </c>
@@ -11764,7 +11482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>97</v>
       </c>
@@ -11814,7 +11532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>97</v>
       </c>
@@ -11864,7 +11582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>97</v>
       </c>
@@ -11914,7 +11632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>97</v>
       </c>
@@ -11964,7 +11682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>97</v>
       </c>
@@ -12014,7 +11732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>97</v>
       </c>
@@ -12064,7 +11782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>97</v>
       </c>
@@ -12114,7 +11832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>97</v>
       </c>
@@ -12164,7 +11882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>97</v>
       </c>
@@ -12214,7 +11932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>97</v>
       </c>
@@ -12264,7 +11982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>97</v>
       </c>
@@ -12314,7 +12032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>97</v>
       </c>
@@ -12364,7 +12082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>97</v>
       </c>
@@ -12414,7 +12132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>97</v>
       </c>
@@ -12464,7 +12182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>97</v>
       </c>
@@ -12514,7 +12232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>97</v>
       </c>
@@ -12564,7 +12282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>97</v>
       </c>
@@ -12614,7 +12332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>97</v>
       </c>
@@ -12664,7 +12382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>97</v>
       </c>
@@ -12714,7 +12432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>97</v>
       </c>
@@ -12764,7 +12482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>97</v>
       </c>
@@ -12814,7 +12532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>97</v>
       </c>
@@ -12864,7 +12582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>97</v>
       </c>
@@ -12914,7 +12632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>97</v>
       </c>
@@ -12964,7 +12682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>97</v>
       </c>
@@ -13014,7 +12732,7 @@
         <v>2.4791666666666665</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>97</v>
       </c>
@@ -13064,7 +12782,7 @@
         <v>2.4791666666666665</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>97</v>
       </c>
@@ -13114,7 +12832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>97</v>
       </c>
@@ -13164,7 +12882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>97</v>
       </c>
@@ -13264,7 +12982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>97</v>
       </c>
@@ -13314,7 +13032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>97</v>
       </c>
@@ -13364,7 +13082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>97</v>
       </c>
@@ -13414,7 +13132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>98</v>
       </c>
@@ -13464,7 +13182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>98</v>
       </c>
@@ -13514,7 +13232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>98</v>
       </c>
@@ -13564,7 +13282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>98</v>
       </c>
@@ -13614,7 +13332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>98</v>
       </c>
@@ -13664,7 +13382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>98</v>
       </c>
@@ -13714,7 +13432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>98</v>
       </c>
@@ -13764,7 +13482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>98</v>
       </c>
@@ -13814,7 +13532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>98</v>
       </c>
@@ -13864,7 +13582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>98</v>
       </c>
@@ -13914,7 +13632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>98</v>
       </c>
@@ -13964,7 +13682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>98</v>
       </c>
@@ -14014,7 +13732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>98</v>
       </c>
@@ -14064,7 +13782,7 @@
         <v>5.1428571428571432</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>98</v>
       </c>
@@ -14114,7 +13832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>98</v>
       </c>
@@ -14164,7 +13882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>98</v>
       </c>
@@ -14214,7 +13932,7 @@
         <v>5.1428571428571432</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>98</v>
       </c>
@@ -14264,7 +13982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>98</v>
       </c>
@@ -14314,7 +14032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>98</v>
       </c>
@@ -14364,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>98</v>
       </c>
@@ -14414,7 +14132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>98</v>
       </c>
@@ -14464,7 +14182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>98</v>
       </c>
@@ -14514,7 +14232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>98</v>
       </c>
@@ -14564,7 +14282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>98</v>
       </c>
@@ -14614,7 +14332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>98</v>
       </c>
@@ -14664,7 +14382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>98</v>
       </c>
@@ -14714,7 +14432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>98</v>
       </c>
@@ -14764,7 +14482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>98</v>
       </c>
@@ -14814,7 +14532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>98</v>
       </c>
@@ -14864,7 +14582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>98</v>
       </c>
@@ -14914,7 +14632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>98</v>
       </c>
@@ -14964,7 +14682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>98</v>
       </c>
@@ -15014,7 +14732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>98</v>
       </c>
@@ -15064,7 +14782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>98</v>
       </c>
@@ -15114,7 +14832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>98</v>
       </c>
@@ -15164,7 +14882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>98</v>
       </c>
@@ -15214,7 +14932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>98</v>
       </c>
@@ -15264,7 +14982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>98</v>
       </c>
@@ -15314,7 +15032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>98</v>
       </c>
@@ -15364,7 +15082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>98</v>
       </c>
@@ -15414,7 +15132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>98</v>
       </c>
@@ -15464,7 +15182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>98</v>
       </c>
@@ -15514,7 +15232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>98</v>
       </c>
@@ -15564,7 +15282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>98</v>
       </c>
@@ -15614,7 +15332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>98</v>
       </c>
@@ -15664,7 +15382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>98</v>
       </c>
@@ -15714,7 +15432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>98</v>
       </c>
@@ -15764,7 +15482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>98</v>
       </c>
@@ -15814,7 +15532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>98</v>
       </c>
@@ -15864,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>98</v>
       </c>
@@ -15914,7 +15632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>98</v>
       </c>
@@ -15964,7 +15682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>98</v>
       </c>
@@ -16014,7 +15732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>98</v>
       </c>
@@ -16064,7 +15782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>98</v>
       </c>
@@ -16114,7 +15832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>98</v>
       </c>
@@ -16164,7 +15882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>98</v>
       </c>
@@ -16214,7 +15932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>98</v>
       </c>
@@ -16314,7 +16032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>98</v>
       </c>
@@ -16364,7 +16082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>98</v>
       </c>
@@ -16414,7 +16132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>98</v>
       </c>
@@ -16464,7 +16182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>99</v>
       </c>
@@ -16514,7 +16232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>99</v>
       </c>
@@ -16564,7 +16282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>99</v>
       </c>
@@ -16614,7 +16332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>99</v>
       </c>
@@ -16664,7 +16382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>99</v>
       </c>
@@ -16714,7 +16432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>99</v>
       </c>
@@ -16764,7 +16482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>99</v>
       </c>
@@ -16814,7 +16532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>99</v>
       </c>
@@ -16864,7 +16582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>99</v>
       </c>
@@ -16914,7 +16632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>99</v>
       </c>
@@ -16964,7 +16682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>99</v>
       </c>
@@ -17014,7 +16732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>99</v>
       </c>
@@ -17064,7 +16782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>99</v>
       </c>
@@ -17114,7 +16832,7 @@
         <v>17.821782178217823</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>99</v>
       </c>
@@ -17164,7 +16882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>99</v>
       </c>
@@ -17214,7 +16932,7 @@
         <v>11.881188118811881</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>99</v>
       </c>
@@ -17264,7 +16982,7 @@
         <v>5.9405940594059405</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>99</v>
       </c>
@@ -17314,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>99</v>
       </c>
@@ -17364,7 +17082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>99</v>
       </c>
@@ -17414,7 +17132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>99</v>
       </c>
@@ -17464,7 +17182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>99</v>
       </c>
@@ -17514,7 +17232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>99</v>
       </c>
@@ -17564,7 +17282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>99</v>
       </c>
@@ -17614,7 +17332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>99</v>
       </c>
@@ -17664,7 +17382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>99</v>
       </c>
@@ -17714,7 +17432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>99</v>
       </c>
@@ -17764,7 +17482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>99</v>
       </c>
@@ -17814,7 +17532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>99</v>
       </c>
@@ -17864,7 +17582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>99</v>
       </c>
@@ -17914,7 +17632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>99</v>
       </c>
@@ -17964,7 +17682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>99</v>
       </c>
@@ -18014,7 +17732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>99</v>
       </c>
@@ -18064,7 +17782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>99</v>
       </c>
@@ -18114,7 +17832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>99</v>
       </c>
@@ -18164,7 +17882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>99</v>
       </c>
@@ -18214,7 +17932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>99</v>
       </c>
@@ -18264,7 +17982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>99</v>
       </c>
@@ -18314,7 +18032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>99</v>
       </c>
@@ -18364,7 +18082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>99</v>
       </c>
@@ -18414,7 +18132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>99</v>
       </c>
@@ -18464,7 +18182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>99</v>
       </c>
@@ -18514,7 +18232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>99</v>
       </c>
@@ -18564,7 +18282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>99</v>
       </c>
@@ -18614,7 +18332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>99</v>
       </c>
@@ -18664,7 +18382,7 @@
         <v>216.78899082568807</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>99</v>
       </c>
@@ -18714,7 +18432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>99</v>
       </c>
@@ -18764,7 +18482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>99</v>
       </c>
@@ -18814,7 +18532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>99</v>
       </c>
@@ -18864,7 +18582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>99</v>
       </c>
@@ -18914,7 +18632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>99</v>
       </c>
@@ -18964,7 +18682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>99</v>
       </c>
@@ -19014,7 +18732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>99</v>
       </c>
@@ -19064,7 +18782,7 @@
         <v>172.27722772277227</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>99</v>
       </c>
@@ -19114,7 +18832,7 @@
         <v>148.51485148514851</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>99</v>
       </c>
@@ -19164,7 +18882,7 @@
         <v>23.762376237623762</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>99</v>
       </c>
@@ -19214,7 +18932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>99</v>
       </c>
@@ -19264,7 +18982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>99</v>
       </c>
@@ -19314,7 +19032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>99</v>
       </c>
@@ -19364,7 +19082,7 @@
         <v>378.89108910891082</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>99</v>
       </c>
@@ -19414,7 +19132,7 @@
         <v>47.524752475247524</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>99</v>
       </c>
@@ -19464,7 +19182,7 @@
         <v>297.02970297029702</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>99</v>
       </c>
@@ -19564,7 +19282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>99</v>
       </c>
@@ -19614,7 +19332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>99</v>
       </c>
@@ -19664,7 +19382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>99</v>
       </c>
@@ -19714,7 +19432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>99</v>
       </c>
@@ -19764,7 +19482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>99</v>
       </c>
@@ -19814,7 +19532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>99</v>
       </c>
@@ -19864,7 +19582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>122</v>
       </c>
@@ -19914,7 +19632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>122</v>
       </c>
@@ -19964,7 +19682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>122</v>
       </c>
@@ -20014,7 +19732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>122</v>
       </c>
@@ -20064,7 +19782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>122</v>
       </c>
@@ -20114,7 +19832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>122</v>
       </c>
@@ -20164,7 +19882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>122</v>
       </c>
@@ -20214,7 +19932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>122</v>
       </c>
@@ -20264,7 +19982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>122</v>
       </c>
@@ -20314,7 +20032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>122</v>
       </c>
@@ -20364,7 +20082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>122</v>
       </c>
@@ -20414,7 +20132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>122</v>
       </c>
@@ -20464,7 +20182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>122</v>
       </c>
@@ -20514,7 +20232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>122</v>
       </c>
@@ -20564,7 +20282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>122</v>
       </c>
@@ -20614,7 +20332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>122</v>
       </c>
@@ -20664,7 +20382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>122</v>
       </c>
@@ -20714,7 +20432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>122</v>
       </c>
@@ -20764,7 +20482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>122</v>
       </c>
@@ -20814,7 +20532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>122</v>
       </c>
@@ -20864,7 +20582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>122</v>
       </c>
@@ -20914,7 +20632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>122</v>
       </c>
@@ -20964,7 +20682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>122</v>
       </c>
@@ -21014,7 +20732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>122</v>
       </c>
@@ -21064,7 +20782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>122</v>
       </c>
@@ -21114,7 +20832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>122</v>
       </c>
@@ -21164,7 +20882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>122</v>
       </c>
@@ -21214,7 +20932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>122</v>
       </c>
@@ -21264,7 +20982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>122</v>
       </c>
@@ -21314,7 +21032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>122</v>
       </c>
@@ -21364,7 +21082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>122</v>
       </c>
@@ -21414,7 +21132,7 @@
         <v>11.881188118811881</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>122</v>
       </c>
@@ -21464,7 +21182,7 @@
         <v>7.1287128712871279</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>122</v>
       </c>
@@ -21514,7 +21232,7 @@
         <v>4.7524752475247523</v>
       </c>
     </row>
-    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>122</v>
       </c>
@@ -21564,7 +21282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>122</v>
       </c>
@@ -21614,7 +21332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>122</v>
       </c>
@@ -21714,7 +21432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>122</v>
       </c>
@@ -21764,7 +21482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>122</v>
       </c>
@@ -21814,7 +21532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>122</v>
       </c>
@@ -21864,7 +21582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>122</v>
       </c>
@@ -21915,13 +21633,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P415" xr:uid="{B30C244E-ED8D-E247-AA44-F3617E2C6815}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Steller Sea Lion"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P415" xr:uid="{B30C244E-ED8D-E247-AA44-F3617E2C6815}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
